--- a/Material bill.xlsx
+++ b/Material bill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64a7da1b5f172022/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IIMSTC HW\Project work\Power-guard-Intelligent-energy-monitoring---IIMSTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A056156E-099B-48F0-8D60-9CCFDA880FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE7B509-7CE8-4255-AA23-E57362BCAC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2120" yWindow="2120" windowWidth="14400" windowHeight="7270" xr2:uid="{1FE66D70-AAB3-45CE-B1E2-EDA9DA4D55E2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{1FE66D70-AAB3-45CE-B1E2-EDA9DA4D55E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -93,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +129,13 @@
       <name val="Amasis MT Pro Black"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -140,7 +145,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -148,12 +153,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="double">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -173,18 +192,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -324,51 +343,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{86E06FA0-1887-411E-8589-E29805AC5D5D}" name="Table6" displayName="Table6" ref="A3:A15" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{86E06FA0-1887-411E-8589-E29805AC5D5D}" name="Table6" displayName="Table6" ref="A3:A15" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A3:A15" xr:uid="{86E06FA0-1887-411E-8589-E29805AC5D5D}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2F49BB91-8412-460D-9CB1-51266E9C1721}" name="S.NO" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{2F49BB91-8412-460D-9CB1-51266E9C1721}" name="S.NO" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4438F67F-C9DD-4DBA-BB56-D6602FBCA5CE}" name="Table7" displayName="Table7" ref="B3:B14" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4438F67F-C9DD-4DBA-BB56-D6602FBCA5CE}" name="Table7" displayName="Table7" ref="B3:B14" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="B3:B14" xr:uid="{4438F67F-C9DD-4DBA-BB56-D6602FBCA5CE}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{C74B63F4-0F8D-4D51-93B7-306D0A8C36E2}" name="Component Name" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{C74B63F4-0F8D-4D51-93B7-306D0A8C36E2}" name="Component Name" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{880FA4C1-6CE6-4122-976A-413204D04749}" name="Table8" displayName="Table8" ref="C3:C14" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{880FA4C1-6CE6-4122-976A-413204D04749}" name="Table8" displayName="Table8" ref="C3:C14" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="C3:C14" xr:uid="{880FA4C1-6CE6-4122-976A-413204D04749}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E3B5BEF6-C735-4421-BD23-A8E714195BB5}" name="Quantity" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{E3B5BEF6-C735-4421-BD23-A8E714195BB5}" name="Quantity" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FBAFA522-F6B7-41C7-8811-070EE5A7BFBE}" name="Table10" displayName="Table10" ref="D3:D14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FBAFA522-F6B7-41C7-8811-070EE5A7BFBE}" name="Table10" displayName="Table10" ref="D3:D14" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="D3:D14" xr:uid="{FBAFA522-F6B7-41C7-8811-070EE5A7BFBE}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{5F902EE8-3276-43D4-9A9A-744FB04A9685}" name="Unit Price (₹)" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{5F902EE8-3276-43D4-9A9A-744FB04A9685}" name="Unit Price (₹)" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{FF490787-6AFF-40EB-B0F3-CCCB37047318}" name="Table11" displayName="Table11" ref="E3:E15" totalsRowCount="1" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{FF490787-6AFF-40EB-B0F3-CCCB37047318}" name="Table11" displayName="Table11" ref="E3:E15" totalsRowCount="1" headerRowDxfId="2" dataDxfId="1">
   <autoFilter ref="E3:E14" xr:uid="{FF490787-6AFF-40EB-B0F3-CCCB37047318}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{87D3245F-26D0-4A88-8E62-36BCD92BE2AF}" name="Total Price (₹)" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="1">
-      <totalsRowFormula>2694</totalsRowFormula>
+    <tableColumn id="1" xr3:uid="{87D3245F-26D0-4A88-8E62-36BCD92BE2AF}" name="Total Price (₹)" totalsRowFunction="custom" dataDxfId="0">
+      <totalsRowFormula>SUM(E5:E14)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -693,18 +712,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96DFE30A-F098-456A-8F10-F8899FCB168E}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="47.45" customHeight="1">
+    <row r="1" spans="1:14" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -712,430 +732,380 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.95">
-      <c r="A3" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" ht="15.95" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.95">
-      <c r="A5" s="3">
+      <c r="F3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>80</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>80</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
+      <c r="F5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>275</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>275</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
+      <c r="F6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>60</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>60</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
+      <c r="F7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>80</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>80</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3">
+      <c r="F8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>60</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>1.5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>90</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="3">
+      <c r="F9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>20</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>20</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3">
+      <c r="F10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>180</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>180</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="3">
+      <c r="F11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>765.45</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>909.73</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="3">
+      <c r="F12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>550</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>550</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="3">
+      <c r="F13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
         <v>450</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
+      <c r="F14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="3">
-        <f>2694</f>
-        <v>2694</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15">
+        <f>SUM(E5:E14)</f>
+        <v>2694.73</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
